--- a/Data/SocialData.xlsx
+++ b/Data/SocialData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\git\SwagLabs_Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07C4236E-A277-4051-8FDB-C99622C4348E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0BF570-AFD0-48DB-9F68-583BAD4AC629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{79774504-8ADB-4346-BF82-54F54734AF80}"/>
   </bookViews>
@@ -442,14 +442,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA845C3-B71C-4B6F-B19D-F2A9ED886664}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" customWidth="1"/>
     <col min="2" max="2" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -457,16 +457,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -474,16 +473,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E5" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
